--- a/job_tracking.xlsx
+++ b/job_tracking.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O234"/>
+  <dimension ref="A1:O351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,7 +536,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>hr@ateam-entertainment.com</t>
+          <t>hr@a.team</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>hr@us-nooro.com</t>
+          <t>hr@nooro-us.com</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/jobs/view/full-stack-developer-secure-cross-platform-applications-25-07289-at-akraya-inc-4345232620?position=7&amp;pageNum=0&amp;refId=XmIvBhx3ZvuKYyQ2MYb4ow%3D%3D&amp;trackingId=8S10KzqwNH766LFe2fG5jw%3D%3D</t>
+          <t>https://ca.linkedin.com/jobs/view/full-stack-developer-secure-cross-platform-applications-25-07289-at-akraya-inc-4345232620?position=8&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=E1D3gazc5J6mgeNJmf8HOw%3D%3D</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,6 @@
           <t>myliara.com</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>hr@myliara.com</t>
@@ -11442,6 +11441,5506 @@
       <c r="O234" t="inlineStr">
         <is>
           <t>2026-05-11 13:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-staff-engineer-platform-engineering-highlevel-1131588</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>HighLevel</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Staff Engineer Platform Engineering</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>gohighlevel.com</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>hr@gohighlevel.com</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-ai-system-software-developer-wealthsimple-technologies-1131572</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Wealthsimple Technologies</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Senior AI System Software Developer</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>wealthsimple.com</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>hr@wealthsimple.com</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-net-developer-advocate-jetbrains-1131563</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>JetBrains</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>.NET Developer Advocate</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>jetbrains.com</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>hr@jetbrains.com</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-manager-platform-engineering-natera-1131552</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Manager Platform Engineering</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>natera.com</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>hr@natera.com</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-staff-product-manager-enterprise-livekit-1131531</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>LiveKit</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Staff Product Manager Enterprise</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>livekit.com</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>hr@livekit.com</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/business-transformation-lead-2090881</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Expion Health</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Business Transformation Lead</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>expionhealth.com</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>hr@expionhealth.com</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/artificial-intelligence/director-of-revenue-systems-and-ai-automation-offshore-2090878</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Caul Group</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Director of Revenue Systems and AI Automation (Offshore)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>caulgroup.com</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>hr@caulgroup.com</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>https://www.skipthedrive.com/job/dev-technology-mid-level-full-stack-react-node-js-developer-1356372/</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Mid-Level Full Stack React/Node.js Developer</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SkipTheDrive</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>unknown.com</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>hr@unknown.com</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>https://www.freelancer.com/projects/software-development/Stock-Trading-Software-Development-40444740</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Freelancer</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Stock Trading Software Development</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Freelancer</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>freelancer.com</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>hr@freelancer.com</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/remote-senior-javascript-developer-at-4theplayer-com-4411195673?position=1&amp;pageNum=0&amp;refId=Q2vfyrHNn5RRG4HZf6Xfpw%3D%3D&amp;trackingId=Z39XTTI%2F6%2FPBxAdW1Xvj2g%3D%3D</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>4ThePlayer.com</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>REMOTE Senior JavaScript Developer</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>4theplayer.com</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>hr@4theplayer.com</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/full-stack-developer-remote-at-crossing-hurdles-4414434540?position=2&amp;pageNum=0&amp;refId=Q2vfyrHNn5RRG4HZf6Xfpw%3D%3D&amp;trackingId=hACJaEnU%2BgBw5Tf%2BR4xj7A%3D%3D</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Crossing Hurdles</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer | Remote</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>crossinghurdles.com</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>hr@crossinghurdles.com</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/full-stack-engineer-remote-at-quik-hire-staffing-4415317303?position=3&amp;pageNum=0&amp;refId=Q2vfyrHNn5RRG4HZf6Xfpw%3D%3D&amp;trackingId=RqxTi4B5fy%2FbUHJYPhEjFQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Quik Hire Staffing</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>quik-hire.com</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>hr@quik-hire.com</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/jobs/view/frontend-engineer-compliance-tech-at-binance-4327782942?position=1&amp;pageNum=0&amp;refId=EfoDZTDxd%2Fgv%2Bmvieejchw%3D%3D&amp;trackingId=KTkhMdJsv2pENC4bfHf4Zg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Frontend Engineer - Compliance Tech</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>binance.com</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>hr@binance.com</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/frontend-engineer-fully-remote-at-bloomtech-inc-4411155045?position=1&amp;pageNum=0&amp;refId=OeRaw4uA4k%2BACFXkFhE4SQ%3D%3D&amp;trackingId=FI2UdZu5wXFl%2FWbcLXdpqA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>BLOOMTECH, Inc</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Frontend Engineer_Fully Remote</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>bloomtech.com</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>hr@bloomtech.com</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/jobs/view/front-end-developer-at-paytech-group-4414773028?position=1&amp;pageNum=0&amp;refId=r3qOZo3GDWqIq9y6BBvO%2BA%3D%3D&amp;trackingId=NMjPSZTg6FpgxHQFSwTm3Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PayTech Group</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Front End Developer</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>paytech-group.com</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>hr@paytech-group.com</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>https://nz.linkedin.com/jobs/view/full-stack-engineer-%E2%80%93-freelance-contract-at-twine-4402454604?position=3&amp;pageNum=0&amp;refId=r3qOZo3GDWqIq9y6BBvO%2BA%3D%3D&amp;trackingId=N3Z93QpZqGyCKBI2EcwTaA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Twine</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer – Freelance Contract</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>twinery.org</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>hr@twinery.org</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/jobs/view/shopify-web-developer-for-anime-jewelry-brand-at-kraymer-art-4414991571?position=1&amp;pageNum=0&amp;refId=7cgGjiSa4cZZakNzdwWcWQ%3D%3D&amp;trackingId=2HYdmOyc0K2iHy2dMUIXqw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Kraymer Art</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Shopify &amp; Web Developer for Anime Jewelry Brand</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>kraymerart.com</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>hr@kraymerart.com</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/jobs/view/full-stack-data-engineer-remote-at-niva-health-4414610330?position=2&amp;pageNum=0&amp;refId=7cgGjiSa4cZZakNzdwWcWQ%3D%3D&amp;trackingId=sIlblgizjLaJrFNhpUydqw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>NIVA Health</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Full-Stack Data Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>nivahealth.com</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>hr@nivahealth.com</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/jobs/view/full-stack-developer-react-node-aws-at-bruntwork-4411500479?position=3&amp;pageNum=0&amp;refId=7cgGjiSa4cZZakNzdwWcWQ%3D%3D&amp;trackingId=twdJyEpDqp5Zm7hQnNHI5A%3D%3D</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>BruntWork</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (React / Node / AWS)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>bruntwork.co</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>hr@bruntwork.co</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/jobs/view/lead-software-engineer-java-full-stack-remote-at-legalmatch-philippines-inc-4414567958?position=4&amp;pageNum=0&amp;refId=7cgGjiSa4cZZakNzdwWcWQ%3D%3D&amp;trackingId=X7VrYouZuwRLY5EEG8R1Jw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>LegalMatch Philippines, Inc.</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Lead Software Engineer: Java Full Stack (Remote)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>legalmatch.ph</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>hr@legalmatch.ph</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>https://vn.linkedin.com/jobs/view/senior-fullstack-developer-reactjs-dotnet-night-shift-at-outsource-solutions-co-ltd-4414663164?position=1&amp;pageNum=0&amp;refId=wMQ7U2iXG3whpY02irhGew%3D%3D&amp;trackingId=g89OTiMtbNXl%2Fj0vXRW0rw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>OUTSOURCE SOLUTIONS CO.,LTD</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SENIOR FULLSTACK DEVELOPER (ReactJs/Dotnet) - Night Shift</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>outsourcesolutions.vn</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>hr@outsourcesolutions.vn</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/frontend-developer-at-ringcentral-4414718625?position=1&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=I4MHU9w2hrOYKjSZAOXxEQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>RingCentral</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>ringcentral.com</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>hr@ringcentral.com</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/frontend-developer-at-recrew-ai-4414590475?position=2&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=R%2FvymJjDoEGsM7qiCnbJPA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Recrew AI</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>recrew.ai</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>hr@recrew.ai</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/frontend-developer-at-careerxperts-consulting-4411163622?position=3&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=1MHJrIYpT2z%2FAztT%2FyE8Pg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>CareerXperts Consulting</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>careerxperts.com</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>hr@careerxperts.com</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/front-end-developer-intern-entry-level-html-%E2%80%A2-css-%E2%80%A2-javascript-remote-at-skillzenloop-4411199380?position=4&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=SbChphQ3CoeUFsUoGx%2BYBw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Skillzenloop</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Front End Developer Intern (Entry Level) | HTML • CSS • JavaScript | Remote</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>skillzenloop.com</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>hr@skillzenloop.com</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/senior-software-engineer-full-stack-fintech-airlines-apac-india-100%25-remote-at-hopper-4373025420?position=6&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=BW1HIFOYjwWQLmzVj1ePgA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Hopper</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack - Fintech Airlines - APAC (India - 100% Remote)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>hopper.com</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>hr@hopper.com</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/front-end-developer-intern-at-infrabyte-consulting-4414976761?position=7&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=zt4fLWbmLlAn7mmmpI06eg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Infrabyte Consulting</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Front-End Developer Intern</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>infrabyteits.com</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>hr@infrabyteits.com</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/javascript-developer-at-fetchjobs-co-4414786743?position=8&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=Sam%2FPlDMuzfAfQRkweeYNg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>FetchJobs.co</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>JavaScript Developer</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>fetchjobs.co</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>hr@fetchjobs.co</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/web-developer-at-brightedge-4414478166?position=9&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=Ll6dnDLfOEQejbzYmYjWRg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>BrightEdge</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Web Developer</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>brightedge.com</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>hr@brightedge.com</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/remote-javascript-developer-at-turing-4414601472?position=10&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=mELGIciL%2Fm6XKeK9Ky7vNw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Remote JavaScript Developer</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>turing.com</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>hr@turing.com</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/html-css-developer-intern-remote-entry-level-web-structuring-responsive-design-at-inficore-soft-4415000521?position=20&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=r%2F9QBGhrnG%2BkKiL0I9VS9w%3D%3D</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Inficore Soft</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HTML/CSS Developer Intern | Remote | Entry-Level | Web Structuring / Responsive Design</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>inficoresoft.com</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>hr@inficoresoft.com</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/hire-alert-e-commerce-full-stack-developer-fresher-at-capacity-web-solutions-pvt-ltd-4411191096?position=42&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=%2BAK%2B77Hh1DeDzeWhDqwndA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Capacity Web Solutions Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HIRE ALERT: E-commerce Full-Stack Developer (Fresher)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>capacitywebsolutions.com</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>hr@capacitywebsolutions.com</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-developer-at-cosmicit-4414457521?position=46&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=zAwMPtIs5pG8Cxila%2FYfzQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>CosMicIT</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>cosmic-it.in</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>hr@cosmic-it.in</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-at-rexus-solutions-4414592610?position=50&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=hXR9ysPFkow%2BTrUDWdN1AA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Rexus Solutions</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>rexussolutions.com</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>hr@rexussolutions.com</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-developer-outbound-selfservice-at-miratech-4411148530?position=52&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=MZCxTdMKlHslkQ7CpMPelQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Miratech</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (Outbound/Selfservice)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>miratechcorp.com</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>hr@miratechcorp.com</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/senior-angular-developer-at-jobgether-4414791961?position=56&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=yBcfdAx8yN0vvSl2gKiGqg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Senior Angular Developer</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>jobgether.com</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>hr@jobgether.com</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-ai-first-developer-at-rapidbrains-4414789869?position=57&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=TSgY3Y8TREIaV7hGiG4k5g%3D%3D</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>RapidBrains</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Full-Stack AI-First Developer</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>rapidbrains.com</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>hr@rapidbrains.com</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/associate-full-stack-developer-at-techolution-4414786673?position=58&amp;pageNum=0&amp;refId=bjJNDdpL2jWmdNG4ISH0Kw%3D%3D&amp;trackingId=mQzCkLyRE0RIrGSPpOZ1pA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>techolution</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Associate Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>techolution.com</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>hr@techolution.com</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/react-developer-contract-usa-at-here-4414709525?position=2&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=NJkuHm%2FtgEJHuWuDsngQ8w%3D%3D</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HERE</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>React Developer (Contract) - USA</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>here.com</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>hr@here.com</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/front-end-developer-next-js-react-remote-at-consultnet-technology-services-and-solutions-4414697110?position=3&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=iU2Et7fZ2lce8JnlZHrRTQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ConsultNet Technology Services and Solutions</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Front-End Developer (Next.js / React)- Remote</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>consultnet.com</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>hr@consultnet.com</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/product-front-end-engineer-%E2%80%93-fully-remote-us-%E2%80%93-competitive-salary-%2B-equity-%2B-opportunity-to-work-with-an-ambitious-rapidly-growing-start-up-at-orbis-group-4411867480?position=5&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=cDbF%2FElRCcTapXLAh5gcAQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Orbis Group</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Product (Front-End) Engineer – Fully Remote (US) – Competitive Salary + Equity + Opportunity to work with an Ambitious, Rapidly-Growing Start-Up</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>orbis.org</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>hr@orbis.org</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-porter-4414790038?position=6&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=Us%2BxGYksKKkiS5Ht04LOsg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Porter</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>porter.in</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>hr@porter.in</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-developer-react-node-js-at-gorin-systems-4414468470?position=7&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=rssfjQq%2Fo7dEz2N05LGJCQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Gorin Systems</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer (React / Node.js)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>gorinsystems.com</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>hr@gorinsystems.com</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/data-engineer-front-end-developer-at-lockheed-martin-4414951013?position=8&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=umsP43FXluZ9WJwo2jbx%2FQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Data Engineer / Front-End Developer</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>lockheedmartin.com</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>hr@lockheedmartin.com</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-humana-4411195480?position=9&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=qey%2BcFPBCT0AcAeZErhigg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>humana.com</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>hr@humana.com</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-developer-at-dataannotation-4374795717?position=11&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=VAUou%2FBEasDBqR%2FV2HQpDg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>dataannotation.tech</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>hr@dataannotation.tech</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-product-engineer-ai-prompt-systems-at-intelligenic-4414748211?position=12&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=EyMMePKFWduUAq16gYu9eA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Intelligenic</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Full-Stack Product Engineer (AI &amp; Prompt Systems)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>intelligenic.ai</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>hr@intelligenic.ai</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-publicis-media-4393054311?position=13&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=yt%2BHYcmOOBOrME1mOxURsQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Publicis Media</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>publicisgroupe.com</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>hr@publicisgroupe.com</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-full-stack-engineer-with-a-love-for-skincare-at-regimenpro-4414667166?position=14&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=1IgO2kt8C5sEUnCdHkloYA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>RegimenPro</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer with a love for skincare</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>regimenpro.com</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>hr@regimenpro.com</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-developer-remote-at-sundayy-4414467685?position=15&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=Ugt%2BfDuvngnwwnpPeoti2Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Sundayy</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Full Stack Developer - Remote</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>sundayy.com</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>hr@sundayy.com</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-software-engineer-at-nextsource-4414591653?position=16&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=TIscL4E0wRQV6eKFh4pfuQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>nextSource</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>nextsource.com</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>hr@nextsource.com</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-full-stack-at-remotehunter-4414773321?position=17&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=GwnAdSxOrfY7upNn2vbu1w%3D%3D</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>RemoteHunter</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Software Engineer (Full-Stack)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>remotehunter.com</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>hr@remotehunter.com</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-developer-us-remote-contractor-at-bold%2Bbeyond-4414946896?position=18&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=B0AAVWSbUVD9Ab5qnLTmKQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Bold+Beyond</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer - US Remote Contractor</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>boldbeyond.com</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>hr@boldbeyond.com</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/associate-full-stack-product-engineer-at-called-4414741567?position=19&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=1kTKguJwIa5Z8kNQHuawWg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Called</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Associate Full Stack Product Engineer</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>called.co</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>hr@called.co</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-fullstack-engineer-at-cloudbeds-4405274000?position=20&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=qjvnNUT%2BLIfDyjiS1qtkHA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Cloudbeds</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Engineer</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>cloudbeds.com</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>hr@cloudbeds.com</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-iii-at-tailored-management-4414920445?position=21&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=VPgK11YBBcb7WlnJgFZwIw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Tailored Management</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>tailoredmanagement.com</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>hr@tailoredmanagement.com</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-full-stack-software-engineer-at-yahoo-4414762515?position=23&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=k7aYCGwn0Vs35qd1QiORjQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>yahoo.io</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>hr@yahoo.io</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-at-kforce-inc-4414951915?position=30&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=BcwGQ9tssbAv8amUuciU5Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Kforce Inc</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>kforce.com</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>hr@kforce.com</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-software-engineer-magento-php-remote-at-clearesult-4411507515?position=38&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=E9M7dyeLdJeko5zVUk1aFg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>CLEAResult</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer (Magento / PHP) - Remote</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>clearesult.com</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>hr@clearesult.com</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-full-stack-engineer-at-earnin-4414921086?position=39&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=0h29SmBqlDI4rbvceMASJg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>EarnIn</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>earnin.com</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>hr@earnin.com</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/frontend-vue-js-developer-contingent-at-aretum-4404436981?position=40&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=OEZYvNaQqd6FsDltpy9zkA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Aretum</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Frontend Vue.js Developer - Contingent</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>aretum.com</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>hr@aretum.com</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-full-stack-developer-tech-lead-at-sectech-solutions-4414488749?position=47&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=ljw3XojLlBppuCuCOb3WmQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Sectech Solutions</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer/Tech Lead</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>sectech.com</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>hr@sectech.com</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-full-stack-developer-at-h3-technologies-llc-4414675279?position=48&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=9RDnSkgqdv1%2BWzuWLy0Wvg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>h3 Technologies, LLC</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>h3-technologies.com</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>hr@h3-technologies.com</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-net2source-n2s-4414922568?position=49&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=i4%2F0kPE58Z4wR7ZTzNa6Ug%3D%3D</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Net2Source (N2S)</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>net2source.com</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>hr@net2source.com</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/senior-software-engineer-full-stack-at-owner-com-4379268638?position=52&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=i22bdG3fvZJVt7j1Ct4Cvg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Owner.com</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full-Stack</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>owner.com</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>hr@owner.com</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-signify-technology-4414737770?position=54&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=eD4LcgwmILM%2BMsJt7GtTfw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Signify Technology</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>signifytechnology.com</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>hr@signifytechnology.com</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/sr-software-engineer-design-engineering-at-benepass-4400477035?position=55&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=lktX0vil8fcropVzzGzXBw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Benepass</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Design Engineering)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>getbenepass.com</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>hr@getbenepass.com</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-remote-at-jobright-ai-4414757848?position=57&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=kWpdH4wyDWyaBGlJEyB3LQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Jobright.ai</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>jobright.ai</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>hr@jobright.ai</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-motion-recruitment-4414626600?position=59&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=hnjgKxTFym30kLFjamvyjg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Motion Recruitment</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>motionrecruitment.com</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>hr@motionrecruitment.com</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/cloud-software-developer-node-js-and-react-js-state-of-louisiana-at-general-dynamics-information-technology-4393580368?position=60&amp;pageNum=0&amp;refId=45PfO%2B7RiCmxUlJj%2B5lk4g%3D%3D&amp;trackingId=cJpPt5U2%2Fc196eEQPG8Trw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Cloud Software Developer (Node.js and React.js) - State of Louisiana</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>gdit.com</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>hr@gdit.com</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/frontend-developer-at-haystack-4411173930?position=1&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=nIgWjFaJq4DOeJQjWEkYmQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Haystack</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>haystackteam.com</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>hr@haystackteam.com</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/frontend-developer-at-hyra-4414490029?position=2&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=GoT8VdqtpkNeRcIEL2QpCw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Hyra</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>hyra.io</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>hr@hyra.io</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/frontend-developer-at-adlib-recruitment-b-corp%E2%84%A2-4411142753?position=3&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=3AmxLcHlcJeKtzOFqvESpA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ADLIB Recruitment | B Corp™</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>adlib-recruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>hr@adlib-recruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/javascript-developer-at-tria-4411172770?position=4&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=rpagWPWCTggjVxE3n5oOfw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>TRIA</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Javascript Developer</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>triafed.com</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>hr@triafed.com</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/software-engineer-front-end-leaning-accessibility-at-synthesia-4373818575?position=6&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=6vkTxRE8uHKkgYcfB738Eg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Synthesia</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Software Engineer, Front End Leaning (Accessibility)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>synthesia.io</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>hr@synthesia.io</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/entry-level-developer-roles-software-web-ai-data-it-product-at-joinrs-4412729864?position=8&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=Qf2v9vXZ588ohNH9NqrvVQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Joinrs</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Entry-Level Developer roles (Software, Web, AI, Data, IT, Product)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>joinrs.com</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>hr@joinrs.com</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/full-stack-engineer-at-techshack-4414641348?position=9&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=1XFERh4w9thIUMJXGRyrhQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>TechShack</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>tech-shack.co</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>hr@tech-shack.co</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/full-stack-engineer-remote-leicester-at-outlier-ai-4411560800?position=10&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=jcjvX7zYSz%2Fh8F8lujZj0A%3D%3D</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Outlier AI</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer (Remote) (Leicester)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>outlier.ai</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>hr@outlier.ai</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/full-stack-engineer-at-wynne-consulting-4414607427?position=11&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=2UFRHsWuN3NLQnK6JoerTg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Wynne Consulting</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>wynne.co</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>hr@wynne.co</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/full-stack-engineer-at-inspiring-search-4414631050?position=13&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=YLtDYGD9UYqL%2FB9HI%2FES9Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Inspiring Search</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>inspiringsearch.com</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>hr@inspiringsearch.com</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/full-stack-engineer-at-sr2-socially-responsible-recruitment-certified-b-corporation%E2%84%A2-4411139827?position=15&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=VsdYk7KjO1gZsGk2gfo1lQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SR2 | Socially Responsible Recruitment | Certified B Corporation™</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>sr2rec.com</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>hr@sr2rec.com</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/%F0%9F%9A%80-full-stack-tech-lead-developers-tech-leads-needed-%E2%80%93-fully-remote-uk-up-to-%C2%A385-000-at-areti-group-b-corp%E2%84%A2-4414560905?position=19&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=tSXT3OJbBElag3PPpB17ag%3D%3D</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Areti Group | B Corp™</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>🚀 Full Stack Tech Lead Developers/Tech Leads Needed – Fully Remote (UK) | Up to £85,000</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>bcorporation.net</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>hr@bcorporation.net</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/senior-full-stack-engineer-at-stealth-it-consulting-4411145702?position=21&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=AUYErwQXH3RRb6qNFq5OMA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Stealth iT Consulting</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>stealth-it.com</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>hr@stealth-it.com</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/senior-full-stack-engineer-net-%2B-react-at-flat-rock-technology-%F0%9F%A7%A9-4414584791?position=23&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=k08hifHhKf7i4nKFzS%2Bfeg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Flat Rock Technology 🧩</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer (.NET + React)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>flatrocktech.com</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>hr@flatrocktech.com</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/net-developer-%E2%80%93-edinburgh-at-noir-4414619325?position=24&amp;pageNum=0&amp;refId=b2y%2BJfg6aFWxoqQtHWiNtw%3D%3D&amp;trackingId=zovoR9bIufNZBrz%2Fhrkg5g%3D%3D</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Noir</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>.NET Developer – Edinburgh</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>noir-music.com</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>hr@noir-music.com</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/full-stack-engineer-f-d-m-at-altagram-group-game-localization-4411141911?position=1&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=SPVdX8HRsKLfI1PSyIxYnQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Altagram Group - Game Localization</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer (f/d/m)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>altagram.com</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>hr@altagram.com</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/full-stack-engineer-at-nooxit-4411139885?position=2&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=qH%2Bs2Pl%2Fgbjs4BR8irtbTQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Nooxit</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>nooxit.com</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>hr@nooxit.com</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/full-stack-webentwickler-w-m-x-at-opta-data-4392825851?position=3&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=NEVY2Dyve4o8L1paoQ8Hyw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>opta data</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Full Stack Webentwickler (w/m/x)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>statsperform.com</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>hr@statsperform.com</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/senior-fullstack-applied-ai-engineer-f-m-x-at-maia-4411552007?position=5&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=xuichso4dk1Y88YXsuCUog%3D%3D</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>MAIA</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Applied AI Engineer (f/m/x)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>trymaia.co</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>hr@trymaia.co</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/senior-angular-developer-m-w-d-at-medifox-dan-4414637911?position=9&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=kS04n266bhzcb%2BSfS1RcLw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>MEDIFOX DAN</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Senior Angular Developer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>medifoxdan.de</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>hr@medifoxdan.de</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/fullstack-developer-m-w-d-konstanz-berlin-oder-remote-at-seitenbau-gmbh-4414978044?position=10&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=bNDkmV9uElReHmlwadAP%2Bg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SEITENBAU GmbH</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (m/w/d) - Konstanz, Berlin oder remote</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>seitenbau.com</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>hr@seitenbau.com</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/sr-full-stack-engineer-at-prodege-llc-4414652058?position=11&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=AeMgDxyVRdV%2ByMjaVVjboA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Prodege, LLC</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>prodege.com</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>hr@prodege.com</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/fullstack-developer-sap-fiori-ui5-m-w-d-remote-deutschlandweit-at-cas-concepts-and-solutions-ag-4414465886?position=12&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=3LNHnpKBXw5eAvFly9ZFnA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CAS Concepts and Solutions AG</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Fullstack Developer SAP Fiori/ UI5 (m/w/d) - remote/deutschlandweit</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>c-a-s.de</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>hr@c-a-s.de</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/senior-fullstack-developer-m-w-d-at-virtual7-gmbh-4383821827?position=14&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=zv2XZOfJzj7jeRHx%2F4j%2FzA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>virtual7 GmbH</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Developer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>virtual7.de</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>hr@virtual7.de</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/typo3-web-developer-in-m-w-d-at-instaffo-4393558774?position=15&amp;pageNum=0&amp;refId=dZZ%2FFKeqNMFoG%2B%2F4IRbiiQ%3D%3D&amp;trackingId=in%2BJc30UoMkbPuAGAdauIg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Instaffo</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>TYPO3 Web-Developer:in (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>instaffo.com</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>hr@instaffo.com</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/fullstack-developer-java-react-at-veem-4411561103?position=1&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=sG052JASn4fk0UD2XQEvog%3D%3D</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Veem</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Fullstack Developer (Java, React)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>veem.com</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>hr@veem.com</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/software-developer-react-node-js-at-autodesk-4414793574?position=2&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=%2FGh4jHd4psP1c0lcfCXjLg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Software Developer (React/Node.js)</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>autodesk.com</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>hr@autodesk.com</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/full-stack-developer-at-schema-app-4414484208?position=6&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=OrxshdBqYvlNMHMgOM1AAQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Schema App</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>schemaapp.com</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>hr@schemaapp.com</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/full-stack-engineer-at-vantage-4369701364?position=7&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=ErBOK0%2BWQFMfC808lcLkEA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Vantage</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>vantagemarkets.com</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>hr@vantagemarkets.com</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/backend-node-js-developer-at-enterprise-solutions-inc-4414468701?position=17&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=OAAh28szEYXbGrLSlt98Lw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Enterprise Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Backend Node.js Developer</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>enterprisesolutioninc.com</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>hr@enterprisesolutioninc.com</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/full-stack-engineer-at-insight-global-4407950482?position=19&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=AF9lTaUr5sYTOvAkmjgQlg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Insight Global</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>insightglobal.com</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>hr@insightglobal.com</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-fullstack-engineer-observability-real-user-monitoring-rum-canada-remote-at-grafana-labs-4405431056?position=20&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=IwDqs37mazaarBW%2BmHMloA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Grafana Labs</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Engineer - Observability Real User Monitoring (RUM) | Canada | Remote</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>grafana.com</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>hr@grafana.com</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/senior-full-stack-developer-at-lightspeed-commerce-4411534246?position=24&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=If94mndVO2gTFnxI0gAkig%3D%3D</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Lightspeed Commerce</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>lightspeedhq.com</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>hr@lightspeedhq.com</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/full-stack-engineer-agentic-ai-at-lazer-technologies-4230116517?position=25&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=XzpBtbpIE5wZw4TzP1J58g%3D%3D</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Lazer Technologies</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Agentic AI</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>lazertechnologies.com</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>hr@lazertechnologies.com</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/fullstack-developer-devops-d%C3%A9veloppeur-euse-full-stack-devops-at-datmos-4414686398?position=26&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=hhv8xZOGDXO%2Ft93tfplKLQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Datmos</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Fullstack Developer / DevOps | Développeur.euse Full-Stack / DevOPS</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>datmos.com</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>hr@datmos.com</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/manager-software-engineering-mobile-platform-at-samsara-4372651002?position=27&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=dP7H%2F%2FrFVWclaJEiPpvQ8g%3D%3D</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Manager, Software Engineering - Mobile Platform</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>samsara.com</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>hr@samsara.com</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/jobs/view/technical-lead-at-descartes-systems-group-4414968213?position=29&amp;pageNum=0&amp;refId=T%2FvgbKvc33VL3bCddKq8Hw%3D%3D&amp;trackingId=NGfsc2wqoKlNXPHDgUe3AA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Descartes Systems Group</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Technical Lead</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>descartes.com</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>hr@descartes.com</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/full-stack-developer-python-react/ltimindtree-limited/18962019</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>LTIMindtree Limited</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Full Stack Developer - Python + React</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>ltm.com</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>hr@ltm.com</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/job-title-react-developer/diverse-lynx-india/19065194</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Diverse Lynx India</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Title React Developer</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>tracxn.com</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>hr@tracxn.com</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/frontend-developer-react/more-retail-limited/18771548</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>More Retail Limited</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Frontend Developer React</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>more.in</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>hr@more.in</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/senior-react-developer/capital-placement-services/19018642</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Capital Placement Services</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Senior React Developer</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>capitalplacementservices.com</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>hr@capitalplacementservices.com</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/frontend-developer-react/ntt-data-americas-inc/18778847</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>NTT Data Americas, Inc.</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Frontend Developer (React)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>us.nttdata.com</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>hr@us.nttdata.com</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-frontend-fullstack-react-developer/idfc-first-bank-limited/18785227</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>IDFC FIRST Bank Limited</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>React Frontend, Fullstack, React Developer</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>idfcfirst.bank.in</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>hr@idfcfirst.bank.in</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/front-end-react-developer-architecture-tooling/bmw-techworks-india/19022744</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BMW Techworks India</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Front-end React developer / Architecture tooling</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>bmwtechworks.in</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>hr@bmwtechworks.in</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer/immenso-tech/19015516</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Immenso tech</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>immensotech.com</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>hr@immensotech.com</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer-with-pc-insurance/people-prime-worldwide/19024123</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>People Prime Worldwide</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>React Developer with P&amp;C Insurance</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>people-prime.com</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>hr@people-prime.com</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer/phyelements/19025321</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>PHYELEMENTS</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>phyelements.com</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>hr@phyelements.com</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:39</t>
         </is>
       </c>
     </row>

--- a/job_tracking.xlsx
+++ b/job_tracking.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O351"/>
+  <dimension ref="A1:O418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,16 @@
           <t>correlation-one.com</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>hr@correlation-one.com</t>
@@ -536,7 +546,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:36</t>
         </is>
       </c>
     </row>
@@ -571,6 +581,16 @@
           <t>akuity.io</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>hr@akuity.io</t>
@@ -583,7 +603,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:36</t>
         </is>
       </c>
     </row>
@@ -618,6 +638,16 @@
           <t>rainfocus.com</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>hr@rainfocus.com</t>
@@ -630,7 +660,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:36</t>
         </is>
       </c>
     </row>
@@ -665,6 +695,16 @@
           <t>grantstreet.com</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>hr@grantstreet.com</t>
@@ -677,7 +717,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:36</t>
         </is>
       </c>
     </row>
@@ -712,6 +752,16 @@
           <t>geotab.com</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>hr@geotab.com</t>
@@ -724,7 +774,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -741,7 +791,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -759,6 +809,16 @@
           <t>sanctuary.computer</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>hr@sanctuary.computer</t>
@@ -771,7 +831,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -806,6 +866,16 @@
           <t>paragon-software.com</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>hr@paragon-software.com</t>
@@ -818,7 +888,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -853,6 +923,16 @@
           <t>ibility.io</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>hr@ibility.io</t>
@@ -865,7 +945,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -882,7 +962,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Freelance Writer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,6 +980,16 @@
           <t>iapwe.org</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>hr@iapwe.org</t>
@@ -912,7 +1002,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -947,6 +1037,16 @@
           <t>parkosecure.ch</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>hr@parkosecure.ch</t>
@@ -959,7 +1059,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -994,6 +1094,16 @@
           <t>coalitiontechnologies.com</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>hr@coalitiontechnologies.com</t>
@@ -1006,7 +1116,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -1041,6 +1151,16 @@
           <t>lemon.io</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>hr@lemon.io</t>
@@ -1053,7 +1173,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -1088,6 +1208,16 @@
           <t>bulldogdm.com</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>hr@bulldogdm.com</t>
@@ -1100,7 +1230,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1247,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Content Reviewer - US</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1135,6 +1265,16 @@
           <t>telusdigital.com</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>hr@telusdigital.com</t>
@@ -1147,7 +1287,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1304,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1182,6 +1322,16 @@
           <t>agents.dryground.ai</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>hr@dryground.ai</t>
@@ -1194,7 +1344,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1361,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Customer Retention Manager</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1229,6 +1379,16 @@
           <t>autohdr.com</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>hr@autohdr.com</t>
@@ -1241,7 +1401,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1276,6 +1436,17 @@
           <t>ateam-entertainment.com</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>hr@a.team</t>
@@ -1288,7 +1459,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:37</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1506,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1523,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🇩🇪 Senior/Staff Software Engineer PHP, TS, Rust, Kotlin (m/w/d)</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1370,6 +1541,16 @@
           <t>easybill.de</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>hr@easybill.de</t>
@@ -1382,7 +1563,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1580,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>iOS Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1417,6 +1598,16 @@
           <t>us-nooro.com</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>hr@nooro-us.com</t>
@@ -1429,7 +1620,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1667,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1714,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1761,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1808,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1855,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1902,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1949,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1996,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1852,7 +2043,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1899,7 +2090,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2137,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2184,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2231,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2278,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2295,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2122,6 +2313,16 @@
           <t>huntst.com</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>hr@huntst.com</t>
@@ -2134,7 +2335,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2382,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2429,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2476,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2523,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2570,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2617,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2634,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Front End Developer Intern (HTML, CSS, JavaScript, React)</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2451,6 +2652,16 @@
           <t>wakeupwhistle.com</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>hr@wakeupwhistle.com</t>
@@ -2463,7 +2674,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2721,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2768,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2815,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2862,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2909,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2956,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2973,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2780,6 +2991,16 @@
           <t>micro1.ai</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>hr@micro1.ai</t>
@@ -2792,7 +3013,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2839,7 +3060,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2856,7 +3077,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>React / Node.js Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2874,6 +3095,16 @@
           <t>digicroz.com</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>hr@digicroz.com</t>
@@ -2886,7 +3117,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2933,7 +3164,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -2980,7 +3211,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3258,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3305,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3352,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3399,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3446,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3493,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3540,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3587,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3634,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3681,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3728,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3775,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3822,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3869,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3916,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3963,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3779,7 +4010,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3826,7 +4057,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3873,7 +4104,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3920,7 +4151,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -3967,7 +4198,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4245,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4292,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4339,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4386,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4433,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4480,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4527,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4574,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4621,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4668,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4715,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4762,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4809,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4856,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4903,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4950,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4997,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4813,7 +5044,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4860,7 +5091,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4907,7 +5138,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -4954,7 +5185,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5232,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5279,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5326,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5373,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5420,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5467,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5514,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5561,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5608,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5655,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5702,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5749,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5766,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lead Fullstack Developer (m/f/d) - TypeScript / Angular / Node.js - PDR.cloud GmbH</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5553,6 +5784,16 @@
           <t>efinancialcareers.com</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>hr@efinancialcareers.com</t>
@@ -5565,7 +5806,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5853,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5900,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5947,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5994,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5800,7 +6041,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5847,7 +6088,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5894,7 +6135,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -5929,6 +6170,16 @@
           <t>liveconnections.in</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>hr@liveconnections.in</t>
@@ -5941,7 +6192,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:30</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6239,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6256,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Frontend React Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6023,6 +6274,16 @@
           <t>kpmg.com</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>hr@kpmg.com</t>
@@ -6035,7 +6296,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6070,6 +6331,16 @@
           <t>page.com</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>hr@page.com</t>
@@ -6082,7 +6353,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6400,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6447,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6494,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6541,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6588,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6605,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Senior UI Specialist - React Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6352,6 +6623,16 @@
           <t>yash.com</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>hr@yash.com</t>
@@ -6364,7 +6645,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6692,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6739,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-05-08 13:42</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6786,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6833,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6880,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6927,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6974,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6740,7 +7021,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6787,7 +7068,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6834,7 +7115,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6881,7 +7162,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6928,7 +7209,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -6975,7 +7256,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7303,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7350,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7397,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7444,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7491,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7538,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7585,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7632,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7679,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7726,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7773,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7820,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7867,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7914,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7961,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7727,7 +8008,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7774,7 +8055,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7821,7 +8102,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7868,7 +8149,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7915,7 +8196,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -7962,7 +8243,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8290,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8337,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8384,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8431,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8478,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8525,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8572,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8619,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8666,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8713,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8760,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8807,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8854,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8901,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8948,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8995,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8761,7 +9042,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8808,7 +9089,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8855,7 +9136,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8902,7 +9183,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8949,7 +9230,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -8996,7 +9277,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9324,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9371,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9418,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9465,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9512,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9559,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9606,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9653,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9700,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9747,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9794,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9841,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9888,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9935,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9982,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9748,7 +10029,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9795,7 +10076,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9842,7 +10123,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9889,7 +10170,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9936,7 +10217,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -9983,7 +10264,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10311,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10358,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10405,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10452,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10499,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10546,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10593,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10640,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10687,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10734,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10781,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10828,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10875,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10922,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10969,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10735,7 +11016,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10782,7 +11063,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10829,7 +11110,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10876,7 +11157,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10923,7 +11204,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -10970,7 +11251,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11298,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11345,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11111,7 +11392,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11439,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11486,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11533,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11580,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11627,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11674,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11721,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2026-05-11 13:12</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11738,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Staff Engineer Platform Engineering</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11475,6 +11756,16 @@
           <t>gohighlevel.com</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>hr@gohighlevel.com</t>
@@ -11487,7 +11778,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11825,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11872,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11919,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11966,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11722,7 +12013,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11769,7 +12060,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11816,7 +12107,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11863,7 +12154,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11910,7 +12201,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -11957,7 +12248,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12004,7 +12295,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12342,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12389,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12436,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12483,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12530,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12577,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12624,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12671,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12718,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12765,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12812,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12859,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12906,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12953,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12709,7 +13000,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12756,7 +13047,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12803,7 +13094,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12850,7 +13141,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12897,7 +13188,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12944,7 +13235,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -12991,7 +13282,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13329,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13085,7 +13376,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13423,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13470,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13517,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13273,7 +13564,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13611,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13658,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13705,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13752,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13508,7 +13799,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13846,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13893,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13940,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13987,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13743,7 +14034,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13760,7 +14051,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Remote</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13778,6 +14069,16 @@
           <t>sundayy.com</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>hr@sundayy.com</t>
@@ -13790,7 +14091,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13837,7 +14138,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13854,7 +14155,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Software Engineer (Full-Stack)</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13872,6 +14173,16 @@
           <t>remotehunter.com</t>
         </is>
       </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>hr@remotehunter.com</t>
@@ -13884,7 +14195,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13931,7 +14242,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -13978,7 +14289,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14336,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14072,7 +14383,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14430,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14477,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14524,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14571,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14277,7 +14588,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Frontend Vue.js Developer - Contingent</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14295,6 +14606,16 @@
           <t>aretum.com</t>
         </is>
       </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>hr@aretum.com</t>
@@ -14307,7 +14628,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14675,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14722,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14769,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14816,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14863,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14910,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14957,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14683,7 +15004,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14730,7 +15051,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14777,7 +15098,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14794,7 +15115,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14812,6 +15133,16 @@
           <t>hyra.io</t>
         </is>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>hr@hyra.io</t>
@@ -14824,7 +15155,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14871,7 +15202,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14918,7 +15249,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -14965,7 +15296,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15343,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15390,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15437,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15153,7 +15484,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15531,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15578,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15625,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15672,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15719,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15766,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15813,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15860,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15576,7 +15907,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15954,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15670,7 +16001,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15717,7 +16048,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15764,7 +16095,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15811,7 +16142,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15858,7 +16189,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15905,7 +16236,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15952,7 +16283,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -15999,7 +16330,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16377,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16424,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16140,7 +16471,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16187,7 +16518,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16565,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16281,7 +16612,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16629,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Agentic AI</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -16316,6 +16647,16 @@
           <t>lazertechnologies.com</t>
         </is>
       </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>hr@lazertechnologies.com</t>
@@ -16328,7 +16669,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16375,7 +16716,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16763,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16810,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16516,7 +16857,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16904,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16921,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Frontend Developer React</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -16598,6 +16939,16 @@
           <t>more.in</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>hr@more.in</t>
@@ -16610,7 +16961,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16657,7 +17008,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16704,7 +17055,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16751,7 +17102,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16798,7 +17149,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16833,6 +17184,16 @@
           <t>immensotech.com</t>
         </is>
       </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>hr@immensotech.com</t>
@@ -16845,7 +17206,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:31</t>
         </is>
       </c>
     </row>
@@ -16862,7 +17223,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>React Developer with P&amp;C Insurance</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -16880,6 +17241,16 @@
           <t>people-prime.com</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>hr@people-prime.com</t>
@@ -16892,7 +17263,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>
@@ -16927,7 +17298,16 @@
           <t>phyelements.com</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>hr@phyelements.com</t>
@@ -16940,7 +17320,3316 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>2026-05-15 13:39</t>
+          <t>2026-05-20 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-database-reliability-engineer-cloudlinux-1131613</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Cloudlinux</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Senior Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>cloudlinux.zendesk.com</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>hr@cloudlinux.zendesk.com</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-cro-manager-growth-optimization-lead-for-us-dtc-company-paired-1131608</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Paired</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Senior CRO Manager Growth Optimization Lead for US DTC Company</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>paired.com</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>hr@paired.com</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-senior-golang-developer-tre-altamira-srl-1131593</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>TRE ALTAMIRA Srl</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Senior Golang Developer</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>site.tre-altamira.com</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>hr@site.tre-altamira.com</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-independent-software-developer-1919265</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>A.Team</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>ateam-entertainment.com</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>hr@ateam-entertainment.com</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-development/senior-full-stack-react-developer-2088711</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Lemon.io</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>lemon.io</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>hr@lemon.io</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/marketing/marketing-manager-content-ai-enablement-2090883</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Expion Health</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Marketing Manager, Content &amp; AI Enablement</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Remotive</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>expionhealth.com</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>hr@expionhealth.com</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/prodevelop-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Prodevelop</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>prodevelop.es</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>hr@prodevelop.es</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/ellow-talent-marketplaces-pvt-java-full-stack-developer</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ellow Talent Marketplaces Pvt</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>ellow.io</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>hr@ellow.io</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/horizon-assset-investments-front-end-developer-full-time-remote</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Horizon Assset Investments</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Front-End Developer (Full-Time, Remote)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>WeWorkRemotely</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>horizonassetinvestments.com</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>hr@horizonassetinvestments.com</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>https://www.skipthedrive.com/job/gofasti-1088-fullstack-react-convex-claude-1355569/</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>1088- Fullstack (React + Convex + Claude)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>SkipTheDrive</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>unknown.com</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>hr@unknown.com</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>https://www.freelancer.com/projects/react-native/Food-Tiffin-Delivery-App</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Freelancer</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Freelancer</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>freelancer.com</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>hr@freelancer.com</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/front-end-developer-at-dataannotation-4304436350?position=1&amp;pageNum=0&amp;refId=oEqjnfhLWaKlF7uOoKIRhg%3D%3D&amp;trackingId=MkPzZPRawuAZ%2BrUv67ntOQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>dataannotation.tech</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>hr@dataannotation.tech</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/jobs/view/full-stack-typescript-engineers-react-node-senior-lead-and-staff-remote-australia-at-thedrivegroup-4415489945?position=4&amp;pageNum=0&amp;refId=oEqjnfhLWaKlF7uOoKIRhg%3D%3D&amp;trackingId=nQGFp%2BgOg8luy9ytdXMJWg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>TheDriveGroup</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Full Stack Typescript Engineers - React/Node (Senior, Lead and Staff) - Remote (Australia)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>thedrivegroup.com.au</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>hr@thedrivegroup.com.au</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/frontend-engineer-fully-remote-at-bloomtech-inc-4412247644?position=1&amp;pageNum=0&amp;refId=wJtzzdJ6Us59svlq47hfhA%3D%3D&amp;trackingId=DFp8IIODiSYfABcgAdZekg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>BLOOMTECH, Inc</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Frontend Engineer_Fully Remote</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>bloomtech.com</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>hr@bloomtech.com</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>https://jp.linkedin.com/jobs/view/full-stack-engineer-autonomous-driving-at-moveez-4415600633?position=3&amp;pageNum=0&amp;refId=wJtzzdJ6Us59svlq47hfhA%3D%3D&amp;trackingId=Q8PknUEs2QuI7iplExFK2Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>MoveEz</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Autonomous Driving</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>mooveez.com</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>hr@mooveez.com</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/jobs/view/senior-full-stack-developer-at-wimmer-solutions-4416087679?position=1&amp;pageNum=0&amp;refId=rWIV3jslQSad%2ByrKGjwrpg%3D%3D&amp;trackingId=lFMfdL%2BLWFFyyV7BnziVNg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Wimmer Solutions</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>wimmersolutions.com</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>hr@wimmersolutions.com</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/jobs/view/net-full-stack-software-engineer-at-atticus-advisory-solutions-inc-4415615525?position=2&amp;pageNum=0&amp;refId=rWIV3jslQSad%2ByrKGjwrpg%3D%3D&amp;trackingId=cI2b3XGHPSHjsd0lKexuzQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Atticus Advisory Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>.NET Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>atticus.ph</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>hr@atticus.ph</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/front-end-developer-intern-html-css-javascript-react-at-argo-intern-4415499808?position=1&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=xx4jSA8hz6%2Fv1Tit09YwOw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ArGo Intern</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>argointern.com</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>hr@argointern.com</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/frontend-developer-at-jobbie-4415619037?position=2&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=UnS%2F14Q%2Bv5EDF6gvK00X6A%3D%3D</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Jobbie</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>jobbie.bot</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>hr@jobbie.bot</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/frontend-developer-at-zetheta-algorithms-private-limited-4415483932?position=3&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=SNRR%2BWkrIKJRZmauvh5psA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Zetheta Algorithms Private Limited</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>zetheta.com</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>hr@zetheta.com</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/html-css-developer-intern-entry-level-html-%E2%80%A2-css-%E2%80%A2-web-design-remote-at-skillzenloop-4412248739?position=4&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=Zx8txXZqC9RIqe4q92HS%2FQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Skillzenloop</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>HTML/CSS Developer Intern (Entry Level) | HTML • CSS • Web Design | Remote</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>skillzenloop.com</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>hr@skillzenloop.com</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/front-end-developer-intern-at-infrabyte-consulting-4416065961?position=5&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=ks%2FvyX8Aptz0MJTx6Xcmwg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Infrabyte Consulting</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>infrabyteits.com</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>hr@infrabyteits.com</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/front-end-developer-intern-remote-entry-level-ui-systems-responsive-web-at-inficore-soft-4415448631?position=7&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=jc0W5UJZzoR0D%2BwJsp4KVA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Inficore Soft</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Front End Developer Intern | Remote | Entry-Level | UI Systems / Responsive Web</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>inficoresoft.com</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>hr@inficoresoft.com</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/frontend-engineer-fully-remote-global-ai-powered-tech-talent-venture-at-skillscapital-4415457402?position=9&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=ioUvlCDLgzAcId3atouIiQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SkillsCapital</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Frontend Engineer (Fully Remote) - Global AI-Powered Tech Talent Venture</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>skillscapital.io</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>hr@skillscapital.io</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/founder-s-office-%E2%80%93-full-stack-ai-ml-ui-engineer-at-craticai-4415611367?position=11&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=PhVwlQ7egH5N4iCIb3sQfg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>CraticAI</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Founder's Office – Full Stack AI/ML UI Engineer</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>craticai.com</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>hr@craticai.com</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/remote-full-stack-developer-at-turing-4358944008?position=13&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=ZOSCRF9jklheHHNstnnuJw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Remote Full-Stack Developer</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>turing.com</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>hr@turing.com</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-developer-at-dusker-ai-4415451259?position=29&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=kHucNkmazF8QGWGsRPUwhg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Dusker AI</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>dusker.ai</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>hr@dusker.ai</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-intern-remote-%E2%80%93-india-at-ai-startup-impact-4415474753?position=39&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=VEn8irhnNAfj0IbMQLhuBw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>AI Startup Impact</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer Intern (Remote – India)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>aistartupimpact.com</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>hr@aistartupimpact.com</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/fullstack-senior-software-engineer-at-jobgether-4415452919?position=40&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=9SnTyEElHMKPiOtAl8h2kA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Jobgether</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>jobgether.com</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>hr@jobgether.com</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-at-naukr-ai-4415464733?position=42&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=YzWU7qpYqKXYRE%2BQfTDw%2FQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Naukr.ai</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>naukr.ai</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>hr@naukr.ai</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-at-ascendr-inc-4415457278?position=44&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=Pz%2FDXYiWVDK%2FIInIb9eqDg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Ascendr, Inc.</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>ascendr.ai</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>hr@ascendr.ai</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-developer-at-fetchjobs-co-4415471800?position=45&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=KDYNGD%2BazgmD7FBLVjDKrg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>FetchJobs.co</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>fetchjobs.in</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>hr@fetchjobs.in</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-at-applaunchpad-4415604140?position=46&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=OEWKm4l%2BtQGgv0O1hc%2FLTQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>AppLaunchpad</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>theapplaunchpad.com</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>hr@theapplaunchpad.com</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/senior-full-stack-developer-mern-stack-at-remotohire-4415499573?position=47&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=U9%2BU9dnTxXq63DXypc4DlQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Remotohire</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer (MERN Stack)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>remotive.com</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>hr@remotive.com</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/associate-full-stack-developer-at-techolution-4415480726?position=48&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=wsiTSRYS9mI3b%2F%2FuSd4kmQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>techolution</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Associate Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>techolution.com</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>hr@techolution.com</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-graphql-nestjs-next-js-%E2%80%93-india-remote-at-stoneboy-4415611185?position=49&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=QGA1KlGZrIpP0Lx1TBrkMQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>STONEBOY</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer (GraphQL, NestJS, Next.js) – India / Remote</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>stoneboyz.com</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>hr@stoneboyz.com</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-remote-at-hire-feed-4416076286?position=51&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=H52DWjBJUojM%2BusqO7k3rw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Hire Feed</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>apps.apple.com</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>hr@apps.apple.com</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/full-stack-engineer-at-sourcebae-4416083876?position=52&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=nCE0F7R22hEmCSoHAkP8hw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Sourcebae</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>sourcebae.com</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>hr@sourcebae.com</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/ai-engineer-and-fullstack-ai-developer-at-red-global-4412279099?position=53&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=8MHNOWh5Rjpy3Gtz4IT70A%3D%3D</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>RED Global</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>AI engineer AND Fullstack AI developer</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>redglobal.com</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>hr@redglobal.com</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/senior-full-stack-engineer-ai-focused-contract-at-gravity-infosolutions-inc-4415464516?position=55&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=wpopygr2U0fCtsD8OU7eSg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Gravity Infosolutions, Inc.</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer (AI-Focused) - Contract</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>gravityinfosolutions.com</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>hr@gravityinfosolutions.com</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/senior-php-developer-6-month-contract-at-fe-fundinfo-4416078544?position=57&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=s6cf1Ere45uKCgNQFAsK5w%3D%3D</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>FE fundinfo</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Senior PHP Developer - 6 Month Contract</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>fefundinfo.com</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>hr@fefundinfo.com</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/jobs/view/fullstack-dot-net-developer-at-kbs-solutions-llc-4415607696?position=58&amp;pageNum=0&amp;refId=HYYL1DykiJ3w%2BTC%2B98EY%2BQ%3D%3D&amp;trackingId=t0aF1qhNvYRgJKeUNyDAaQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>KBS Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>FullStack Dot Net Developer</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>kbs-s.com</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>hr@kbs-s.com</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-software-engineer-%E2%80%94-ui-ux-focused-at-psyecology-inc-4415467531?position=50&amp;pageNum=0&amp;refId=5eK2YPZiifA0YDwxbUrHUw%3D%3D&amp;trackingId=a7UHwRO%2B%2BQq9ZafvpyqPGA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>PsyEcology Inc.</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer — UI/UX Focused</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>journals.sagepub.com</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>hr@journals.sagepub.com</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/full-stack-engineer-at-connect-ai-4416045502?position=57&amp;pageNum=0&amp;refId=5eK2YPZiifA0YDwxbUrHUw%3D%3D&amp;trackingId=qAwiHEgBhCmjsO7pEoxkSg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Connect-AI</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>docs.connect.ai</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>hr@docs.connect.ai</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/frontend-developer-at-haystack-4412241371?position=1&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=XpvZGUpt7%2F4LP1Gxz3Qm9w%3D%3D</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Haystack</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>haystack.tv</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>hr@haystack.tv</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/front-end-developer-%E2%80%93-home-based-at-vita-cv-4413958560?position=3&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=0vZ%2F1ODHqHXsQbOlQOvJIQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>VITA CV</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>vitacv.com</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>hr@vitacv.com</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/senior-full-stack-software-engineer-at-reversinglabs-4283761912?position=4&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=T40U4FxXb7h17punB5J0Pg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ReversingLabs</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>reversinglabs.com</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>hr@reversinglabs.com</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/web-developer-at-netrolynx-ai-4416078887?position=6&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=SrPQP0%2BDsv5j3avJR%2BMiPQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Netrolynx AI</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>neurolynxglobal.com</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>hr@neurolynxglobal.com</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/entry-level-developer-roles-software-web-ai-data-it-product-at-joinrs-4416099358?position=8&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=kDfxzhjPJ0H2%2Bd%2Fcw3b%2BzQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Joinrs</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>joinrs.com</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>hr@joinrs.com</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/full-stack-engineer-at-develop-4412261705?position=9&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=eXw5N5A%2B0S%2FGRhvJk0ShJw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>develop</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>canva.com</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>hr@canva.com</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/java-full-stack-developer-sc-eligible-at-stealth-it-consulting-4402861565?position=23&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=XM5YrrF48wgSCST00bCuKg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Stealth iT Consulting</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer (SC Eligible)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>stealth-it.com</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>hr@stealth-it.com</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/jobs/view/senior-software-engineer-backend-growth-platform-at-kraken-4324688631?position=27&amp;pageNum=0&amp;refId=LpXveF6rR5%2BHaM2qYEr19Q%3D%3D&amp;trackingId=vRJpqhehpOG2ujFReHZ%2BSA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend - Growth Platform</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>kraken.com</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>hr@kraken.com</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/senior-full-stack-developer-react-fastapi-django-frontend-affinity-m-f-d-at-mika-ai-4412230184?position=1&amp;pageNum=0&amp;refId=6dfFUxsf9O%2Fz1gm3ZZ3jaQ%3D%3D&amp;trackingId=jULDtQ9s1YKv5WPW5k%2BWog%3D%3D</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>mika AI</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer React/FastAPI/Django (Frontend-Affinity) (m/f/d)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>app.mikalabs.org</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>hr@app.mikalabs.org</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/full-stack-developer-java-react-f-m-d-at-ecosio-4385317649?position=2&amp;pageNum=0&amp;refId=6dfFUxsf9O%2Fz1gm3ZZ3jaQ%3D%3D&amp;trackingId=MZ1EjCmYj%2BlswOLIepGrEw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ecosio</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Full Stack Developer - Java &amp; React (f/m/d)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>ecosio.com</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>hr@ecosio.com</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/full-stack-engineer-at-agilegrid-solutions-4416089198?position=3&amp;pageNum=0&amp;refId=6dfFUxsf9O%2Fz1gm3ZZ3jaQ%3D%3D&amp;trackingId=fMXiWUEJ4qmezW3z4Nc60g%3D%3D</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>AgileGrid Solutions</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>agilitygrid.com</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>hr@agilitygrid.com</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/frontendentwickler-m-w-d-ref-nr-46730-at-wavestone-4412257505?position=4&amp;pageNum=0&amp;refId=6dfFUxsf9O%2Fz1gm3ZZ3jaQ%3D%3D&amp;trackingId=7Gp25kOGwYvZ4sTzk0JrLw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Wavestone</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Frontendentwickler (m/w/d) (Ref.Nr.: 46730)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>wavestone.com</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>hr@wavestone.com</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/lead-fullstack-developer-m-f-d-%E2%80%93-typescript-angular-node-js-at-instaffo-4343762434?position=5&amp;pageNum=0&amp;refId=6dfFUxsf9O%2Fz1gm3ZZ3jaQ%3D%3D&amp;trackingId=TY38ZoOnVMThhIasI8bjIA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Instaffo</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Lead Fullstack Developer (m/f/d) – TypeScript / Angular / Node.js</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>instaffo.com</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>hr@instaffo.com</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>https://de.linkedin.com/jobs/view/net-software-engineer-m-f-d-munich-at-code-compass-%F0%9F%A7%AD-4412264089?position=8&amp;pageNum=0&amp;refId=6dfFUxsf9O%2Fz1gm3ZZ3jaQ%3D%3D&amp;trackingId=hnxY%2FRDReJWXUinkx%2BTczA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Code Compass 🧭</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>codecompass.net</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>hr@codecompass.net</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/lead-frontend-react-developer/hclsoftware/19040737</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>HCLSoftware</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Lead Frontend React Developer</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>hcl-software.com</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>hr@hcl-software.com</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer-experienced/quantbit-technologies-pvt-ltd/19029469</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Quantbit Technologies PVT LTD</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>React Developer Experienced</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>quantbit.io</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>hr@quantbit.io</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/full-stack-react-developer-remote/willware-technologies-private-limited/19038520</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>WILLWARE TECHNOLOGIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Full Stack React Developer (Remote)</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>willwaretech.com</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>hr@willwaretech.com</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer/philodesign-technologies-inc/19058672</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>philodesign technologies inc</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>philodesigntech.com</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>hr@philodesigntech.com</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer/technovert/19043414</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Technovert</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>React Developer</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>technovert.in</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>hr@technovert.in</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer/vishal-yadav/19054226</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Vishal Yadav</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>React developer</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>vishalyadav.cv</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>hr@vishalyadav.cv</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/senior-react-developer/aqilea-formerly-soltia/19042686</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Aqilea formerly Soltia</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Senior React Developer</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>aqilea.com</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>hr@aqilea.com</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-developer-sr-react-developer/anteelo/19053588</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Anteelo</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>React Developer / Sr. React Developer</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>antelo.co.za</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>hr@antelo.co.za</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>https://www.shine.com/jobs/react-native-react-developer/innova-esi/19059553</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Innova ESI</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>React Native + React Developer</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Shine</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>innovaesi.com</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>hr@innovaesi.com</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>2026-05-20 12:29</t>
         </is>
       </c>
     </row>

--- a/job_tracking.xlsx
+++ b/job_tracking.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12915,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14625,7 +14625,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15651,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16791,7 +16791,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17874,7 +17874,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18387,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18615,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18672,7 +18672,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19698,7 +19698,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20211,7 +20211,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20268,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20781,7 +20781,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21123,7 +21123,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21237,7 +21237,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21465,7 +21465,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21921,7 +21921,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -21978,7 +21978,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22035,7 +22035,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22528,7 +22528,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22944,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23105,7 +23105,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23276,7 +23276,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23437,7 +23437,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23541,7 +23541,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23806,7 +23806,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23863,7 +23863,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23910,7 +23910,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -23967,7 +23967,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24024,7 +24024,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24081,7 +24081,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24138,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24195,7 +24195,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24252,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24594,7 +24594,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24698,7 +24698,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24869,7 +24869,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24926,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -24983,7 +24983,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25154,7 +25154,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25211,7 +25211,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25315,7 +25315,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25372,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25429,7 +25429,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25476,7 +25476,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25533,7 +25533,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25704,7 +25704,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25761,7 +25761,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>2026-08-03 18:08</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25875,7 +25875,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>2026-08-03 18:08</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>2026-08-03 18:08</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>2026-08-03 18:08</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>2026-08-03 18:08</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26103,7 +26103,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>2026-08-03 18:09</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26160,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>2026-08-03 18:09</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26217,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>2026-08-03 18:09</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>2026-08-03 18:09</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26502,7 +26502,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26616,7 +26616,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26673,7 +26673,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>2026-08-03 18:10</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26720,7 +26720,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>2026-08-03 18:11</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>2026-08-03 18:11</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26928,7 +26928,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -26985,7 +26985,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>2026-08-03 18:11</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>2026-08-03 18:11</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27099,7 +27099,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>2026-08-03 18:11</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27213,7 +27213,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27270,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27317,7 +27317,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27374,7 +27374,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27592,7 +27592,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>2026-08-03 18:12</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>2026-08-03 18:13</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>2026-08-03 18:13</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27753,7 +27753,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27810,7 +27810,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>2026-08-03 18:13</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>2026-08-03 18:13</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27924,7 +27924,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>2026-08-03 18:13</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>2026-08-03 18:14</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>2026-08-03 18:14</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>2026-08-03 18:14</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28152,7 +28152,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>2026-08-03 18:14</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28246,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>2026-08-03 18:14</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28407,7 +28407,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>2026-08-03 18:14</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28464,7 +28464,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>2026-08-03 18:15</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28511,7 +28511,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>2026-08-03 18:07</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28568,7 +28568,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>2026-08-03 18:15</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28625,7 +28625,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>2026-08-03 18:16</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>2026-08-03 18:16</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28739,7 +28739,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>2026-08-03 18:08</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28796,7 +28796,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>2026-08-03 18:16</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28853,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>2026-08-03 18:16</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>2026-08-03 18:16</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29024,7 +29024,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29195,7 +29195,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29309,7 +29309,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>2026-08-03 18:17</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29423,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29480,7 +29480,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29765,7 +29765,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>2026-08-03 18:18</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29822,7 +29822,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>2026-08-03 18:19</t>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>
@@ -29857,7 +29857,6 @@
           <t>srrecruiters.in</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr">
         <is>
           <t>Y</t>
@@ -29880,7 +29879,148 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>2026-08-03 18:19</t>
+          <t>2026-08-04 12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/micro1/jobs/python-developer-9928524976</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Himalayas</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>micro1.ai</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>support@micro1.ai</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>2026-08-04 12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/backblaze/jobs/developer-advocate</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Backblaze</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Developer Advocate</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Himalayas</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>backblaze.com</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>partnercontact@backblaze.com</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>2026-08-04 12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/netbird/remote-developer-relations-engineer-457229</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>NetBird</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Developer Relations Engineer</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Berlin/Remote</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>netbird.io</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>john.doe@company.com</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>2026-08-04 12:37</t>
         </is>
       </c>
     </row>

--- a/job_tracking.xlsx
+++ b/job_tracking.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O524"/>
+  <dimension ref="A1:O541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12915,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14511,7 +14511,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14625,7 +14625,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -14967,7 +14967,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15366,7 +15366,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15651,7 +15651,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -15993,7 +15993,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16791,7 +16791,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17874,7 +17874,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18387,7 +18387,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18615,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18672,7 +18672,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19014,7 +19014,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19413,7 +19413,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19527,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19698,7 +19698,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19812,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20097,7 +20097,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20211,7 +20211,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20268,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20439,7 +20439,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20781,7 +20781,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21123,7 +21123,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21237,7 +21237,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21408,7 +21408,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21465,7 +21465,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21921,7 +21921,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -21978,7 +21978,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22035,7 +22035,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22253,7 +22253,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="O386" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22471,7 +22471,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22528,7 +22528,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22632,7 +22632,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22944,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23048,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23105,7 +23105,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23276,7 +23276,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23437,7 +23437,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23541,7 +23541,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23635,7 +23635,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23749,7 +23749,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23806,7 +23806,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23863,7 +23863,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23910,7 +23910,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -23967,7 +23967,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24024,7 +24024,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24081,7 +24081,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24138,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24195,7 +24195,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24252,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24594,7 +24594,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24698,7 +24698,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24869,7 +24869,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24926,7 +24926,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -24983,7 +24983,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25154,7 +25154,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25211,7 +25211,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25315,7 +25315,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25372,7 +25372,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25429,7 +25429,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25476,7 +25476,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25533,7 +25533,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25704,7 +25704,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25761,7 +25761,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25875,7 +25875,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26103,7 +26103,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26160,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26217,7 +26217,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26388,7 +26388,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26502,7 +26502,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26559,7 +26559,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26616,7 +26616,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26673,7 +26673,7 @@
       </c>
       <c r="O463" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26720,7 +26720,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26928,7 +26928,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -26985,7 +26985,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27099,7 +27099,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27156,7 +27156,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27213,7 +27213,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27270,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27317,7 +27317,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27374,7 +27374,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27535,7 +27535,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27592,7 +27592,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27649,7 +27649,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27706,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27753,7 +27753,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27810,7 +27810,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27867,7 +27867,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27924,7 +27924,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28095,7 +28095,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28152,7 +28152,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28246,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28407,7 +28407,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28464,7 +28464,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28511,7 +28511,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28568,7 +28568,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28625,7 +28625,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28682,7 +28682,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28739,7 +28739,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28796,7 +28796,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28853,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29024,7 +29024,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29195,7 +29195,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29309,7 +29309,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29423,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29480,7 +29480,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29708,7 +29708,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29765,7 +29765,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29822,7 +29822,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29879,7 +29879,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:45</t>
         </is>
       </c>
     </row>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -29914,6 +29914,16 @@
           <t>micro1.ai</t>
         </is>
       </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M522" t="inlineStr">
         <is>
           <t>support@micro1.ai</t>
@@ -29926,7 +29936,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:46</t>
         </is>
       </c>
     </row>
@@ -29943,7 +29953,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Developer Advocate</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -29961,6 +29971,16 @@
           <t>backblaze.com</t>
         </is>
       </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M523" t="inlineStr">
         <is>
           <t>partnercontact@backblaze.com</t>
@@ -29973,7 +29993,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:46</t>
         </is>
       </c>
     </row>
@@ -29990,7 +30010,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Developer Relations Engineer</t>
+          <t>Senior Frontend Developer</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -30008,9 +30028,19 @@
           <t>netbird.io</t>
         </is>
       </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>john.doe@company.com</t>
+          <t>support@DomainsNext.com</t>
         </is>
       </c>
       <c r="N524" t="inlineStr">
@@ -30020,7 +30050,977 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>2026-08-04 12:37</t>
+          <t>2026-08-04 17:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-business-development-representative-anz-jfrog-1135994</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>JFrog</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>jfrog.com</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>pr@jfrog.com</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-cleansing-crew-operators-indigenousx-1136017</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>IndigenousX</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>indigenousx.com</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>domains@HugeDomains.com</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-bms-service-technician-johnson-controls-1135997</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>RemoteOK</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>johnsoncontrols.com</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>inquiry@jci.com</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/clover-health/jobs/senior-manager-service-operations</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Clover Health</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Himalayas</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>cloverhealth.com</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>agents@cloverhealth.com</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>https://himalayas.app/companies/leaflink/jobs/senior-backend-engineer-ii-marketplace-4638821253</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>LeafLink</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Himalayas</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>leaflink.com</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>support@leaflink.com</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/finom/senior-ios-developer-remote-germany-378396</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Finom</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>finom.co</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>hello@finom.co</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/market-cloud/salesforce-omnistudio-developer-eschborn-194484</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Market Cloud</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Arbeitnow</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Eschborn</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>salesforce.com</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>essupportapac@salesforce.com</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>https://jobicy.com/jobs/142468-senior-software-engineer-product-engineering-eu</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Jobicy</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>ashby.io</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>delta.mu.alpha@gmail.com</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8099277</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Canada - Remote (ON, AB, BC, or NS Only)</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>instacart.com</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>stores@Instacart.com</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>https://careers.datadoghq.com/detail/8082007/?gh_jid=8082007</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>London, United Kingdom; United Kingdom, Remote</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>datadoghq.com</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>info@datadoghq.com</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6128165004</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>mercury.com</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>help@mercury.com</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/ionq/jobs/6130374004</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>IonQ</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Remote, US</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>ionq.com</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>jobs@ionq.com</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/supabase/f048dd68-63f8-4f98-9860-3d5a43c09a01</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Supabase</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>supabase.com</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>security@supabase.com</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/render/b7508c39-c91f-405a-bdef-9c6b6eca1fee</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Render</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Remote: United States</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>render.com</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>support@render.com</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/confluent/46f3f467-8728-47b4-8fad-06e18ffbe552</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Confluent</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Remote, United States</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>confluent.io</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>info@confluent.io</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>https://snout.com/</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Snout</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>HN Who Is Hiring</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Remote US or Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>snout.com</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>support@snout.com</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>https://www.temporal.io/careers</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Temporal Technologies</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Senior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>HN Who Is Hiring</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>temporal.com</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>support@temporal.io</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>Find HR from job URL; type email in HR email column, then run: python3 main.py --sync-from-xlsx</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:49</t>
         </is>
       </c>
     </row>
